--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/05_Releasehistorie.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/05_Releasehistorie.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="1" r:id="Rd67065b8ec974784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kundenstaende" sheetId="2" r:id="R8c2ce17ac34b4c95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="1" r:id="Reda70dd0908c4bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kundenstaende" sheetId="2" r:id="Rd7d7039e2c424212"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/05_Releasehistorie.xlsx
+++ b/testakten/kurpfalz-taxware-software-ip-insolvenz/02_Unternehmen_Produkt/05_Releasehistorie.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="1" r:id="Reda70dd0908c4bbb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kundenstaende" sheetId="2" r:id="Rd7d7039e2c424212"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Releases" sheetId="1" r:id="R7b02d4dbc619497d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kundenstaende" sheetId="2" r:id="R26fe741a0f2f4ee7"/>
   </x:sheets>
 </x:workbook>
 </file>
